--- a/personal_projects/productivity_logs/logs.xlsx
+++ b/personal_projects/productivity_logs/logs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bagim\Desktop\My_projects\personal_projects\productivity_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B12BCE6-EBF8-4654-9A2D-1B59C3DF2A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950F79F7-35C0-44E7-9EEB-CE16FF3389E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,13 +537,11 @@
         <v>45926</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>45927</v>
-      </c>
+      <c r="A24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/personal_projects/productivity_logs/logs.xlsx
+++ b/personal_projects/productivity_logs/logs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bagim\Desktop\My_projects\personal_projects\productivity_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950F79F7-35C0-44E7-9EEB-CE16FF3389E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3023DE2A-EFF4-4195-90D1-9D4BB666CDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,7 +349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -541,7 +541,76 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>45928</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>45933</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>45934</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
